--- a/quality_surveys/002_school_quality_survey--quality_surveys.xlsx
+++ b/quality_surveys/002_school_quality_survey--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfactory'}</t>
+          <t>very satisfactory</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'fairly_satisfactory'}</t>
+          <t>fairly_satisfactory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'fairly_satisfactory'}</t>
+          <t>fairly satisfactory</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsatisfactory'}</t>
+          <t>very_unsatisfactory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'very_unsatisfactory'}</t>
+          <t>very unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'small'}</t>
+          <t>small</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'large'}</t>
+          <t>large</t>
         </is>
       </c>
     </row>
